--- a/data/trans_camb/P1402-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P1402-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6,69</t>
+          <t>7,01</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,68</t>
+          <t>3,79</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5,24</t>
+          <t>5,41</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 6,93</t>
+          <t>-0,78; 7,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 7,33</t>
+          <t>-0,61; 7,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,98; 11,0</t>
+          <t>3,07; 10,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 6,29</t>
+          <t>-1,47; 6,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 5,22</t>
+          <t>-2,38; 4,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 6,65</t>
+          <t>-0,02; 6,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,15; 5,34</t>
+          <t>0,31; 5,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 5,12</t>
+          <t>-0,4; 4,9</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,46; 7,64</t>
+          <t>2,75; 8,1</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>165,4%</t>
+          <t>173,34%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>129,68%</t>
+          <t>133,95%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-14,71; 285,71</t>
+          <t>-25,96; 280,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-12,83; 269,1</t>
+          <t>-16,49; 267,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>47,91; 474,91</t>
+          <t>46,77; 399,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-29,77; 257,31</t>
+          <t>-29,09; 286,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-39,73; 271,37</t>
+          <t>-45,11; 189,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-7,35; 287,13</t>
+          <t>-5,77; 273,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,7; 177,01</t>
+          <t>2,95; 195,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-8,31; 179,9</t>
+          <t>-13,08; 172,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>38,86; 257,8</t>
+          <t>47,62; 293,39</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,8</t>
+          <t>2,76</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,21</t>
+          <t>-0,38</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,28</t>
+          <t>1,17</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 5,08</t>
+          <t>-1,14; 5,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 5,46</t>
+          <t>-0,9; 5,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 6,0</t>
+          <t>-0,68; 5,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 6,17</t>
+          <t>-1,11; 6,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 6,01</t>
+          <t>-1,6; 6,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 3,07</t>
+          <t>-3,88; 2,34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 4,58</t>
+          <t>-0,27; 4,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,02; 5,14</t>
+          <t>-0,07; 4,88</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 3,61</t>
+          <t>-1,03; 3,31</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>53,02%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-2,41%</t>
+          <t>-4,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>16,87%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-18,75; 137,17</t>
+          <t>-19,46; 137,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,81; 148,94</t>
+          <t>-12,74; 148,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,88; 162,24</t>
+          <t>-15,52; 146,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,27; 90,33</t>
+          <t>-11,68; 91,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-15,07; 87,26</t>
+          <t>-16,33; 93,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-32,35; 46,96</t>
+          <t>-34,42; 33,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 75,47</t>
+          <t>-4,04; 84,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 88,73</t>
+          <t>-0,89; 84,24</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-10,36; 61,63</t>
+          <t>-13,35; 58,48</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5,12</t>
+          <t>5,01</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,52</t>
+          <t>2,43</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3,77</t>
+          <t>3,66</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 8,38</t>
+          <t>0,78; 9,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 2,31</t>
+          <t>-4,85; 2,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,18; 9,06</t>
+          <t>1,04; 8,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 8,04</t>
+          <t>-0,68; 8,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 4,51</t>
+          <t>-3,48; 4,59</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 6,22</t>
+          <t>-1,17; 5,95</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,99; 7,07</t>
+          <t>0,77; 7,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 2,38</t>
+          <t>-2,88; 2,42</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,91; 6,35</t>
+          <t>0,9; 6,12</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>58,5%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-6,49; 212,84</t>
+          <t>7,17; 226,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-57,56; 59,35</t>
+          <t>-59,54; 57,51</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13,23; 238,85</t>
+          <t>8,86; 229,42</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-14,18; 160,95</t>
+          <t>-10,06; 175,43</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-40,5; 88,77</t>
+          <t>-41,44; 93,54</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-13,79; 121,7</t>
+          <t>-12,8; 127,41</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,61; 145,67</t>
+          <t>9,34; 141,46</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-40,34; 49,56</t>
+          <t>-39,13; 50,2</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12,74; 130,89</t>
+          <t>9,78; 120,18</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4,27</t>
+          <t>4,2</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,18</t>
+          <t>1,47</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,88</t>
+          <t>2,77</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 4,78</t>
+          <t>-1,52; 4,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,93; 11,42</t>
+          <t>3,85; 11,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,1; 7,89</t>
+          <t>0,73; 7,92</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 6,38</t>
+          <t>-0,51; 6,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 4,9</t>
+          <t>-2,02; 4,56</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 2,97</t>
+          <t>-1,56; 3,99</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,14; 5,05</t>
+          <t>-0,37; 4,65</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,99; 7,14</t>
+          <t>1,66; 6,97</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 4,12</t>
+          <t>0,42; 4,87</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>55,1%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-27,29; 147,79</t>
+          <t>-23,96; 180,19</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>58,9; 355,04</t>
+          <t>58,91; 366,76</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16,27; 259,22</t>
+          <t>3,71; 234,21</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-11,79; 154,75</t>
+          <t>-9,82; 149,05</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-30,34; 120,13</t>
+          <t>-30,5; 118,27</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-42,87; 75,35</t>
+          <t>-22,48; 100,72</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,58; 130,14</t>
+          <t>-6,57; 116,25</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>33,03; 175,49</t>
+          <t>25,6; 170,24</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-10,6; 98,19</t>
+          <t>5,88; 119,28</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3,3</t>
+          <t>2,55</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,47</t>
+          <t>3,02</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3,52</t>
+          <t>2,87</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 9,02</t>
+          <t>-1,21; 8,92</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 4,86</t>
+          <t>-3,24; 4,94</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 7,75</t>
+          <t>-1,78; 6,45</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 9,1</t>
+          <t>-2,8; 9,18</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 5,13</t>
+          <t>-6,66; 5,04</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 8,61</t>
+          <t>-2,32; 7,53</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 7,75</t>
+          <t>-0,43; 7,1</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 3,87</t>
+          <t>-3,79; 3,43</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 6,68</t>
+          <t>-0,89; 5,97</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>37,64%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-24,07; 258,0</t>
+          <t>-17,8; 249,25</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-51,62; 135,59</t>
+          <t>-45,43; 138,87</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-16,03; 233,84</t>
+          <t>-24,87; 178,49</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-25,02; 139,59</t>
+          <t>-24,8; 149,96</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-48,16; 89,85</t>
+          <t>-51,14; 83,5</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-13,74; 138,15</t>
+          <t>-16,91; 125,55</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 133,83</t>
+          <t>-4,76; 124,95</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-38,17; 68,97</t>
+          <t>-41,23; 58,67</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 120,34</t>
+          <t>-10,66; 112,81</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8,94</t>
+          <t>8,99</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,87</t>
+          <t>6,04</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>7,46</t>
+          <t>7,55</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 6,92</t>
+          <t>-1,57; 6,39</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 5,76</t>
+          <t>-1,82; 5,42</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5,19; 13,31</t>
+          <t>5,01; 13,11</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2,1; 10,45</t>
+          <t>1,88; 10,47</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 7,24</t>
+          <t>-1,29; 7,19</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,28; 9,47</t>
+          <t>2,24; 8,82</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,53; 7,41</t>
+          <t>1,35; 7,36</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 5,13</t>
+          <t>-0,18; 5,34</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>4,56; 10,23</t>
+          <t>4,96; 10,29</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>178,58%</t>
+          <t>179,47%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>139,5%</t>
+          <t>143,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>162,09%</t>
+          <t>163,93%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-28,03; 196,75</t>
+          <t>-25,51; 191,7</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-30,34; 178,04</t>
+          <t>-29,84; 164,15</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>68,09; 412,21</t>
+          <t>66,18; 418,37</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>28,9; 387,63</t>
+          <t>21,09; 428,75</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-19,87; 297,16</t>
+          <t>-26,11; 274,59</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>28,57; 413,98</t>
+          <t>29,98; 354,34</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>21,58; 211,6</t>
+          <t>21,68; 215,4</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 151,01</t>
+          <t>-4,28; 152,69</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>71,49; 312,19</t>
+          <t>78,51; 316,35</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2,62</t>
+          <t>3,12</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-2,9</t>
+          <t>-0,98</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-0,49</t>
+          <t>1,0</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 4,95</t>
+          <t>-1,15; 4,84</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1,64; 8,02</t>
+          <t>1,68; 8,15</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 5,57</t>
+          <t>-0,08; 5,89</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 3,96</t>
+          <t>-2,06; 3,55</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 4,37</t>
+          <t>-1,9; 4,38</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-7,05; -0,19</t>
+          <t>-3,66; 1,36</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 3,4</t>
+          <t>-0,81; 3,24</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,84; 5,24</t>
+          <t>0,78; 5,47</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 1,51</t>
+          <t>-0,82; 2,98</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>48,37%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-37,97%</t>
+          <t>-12,85%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-6,94%</t>
+          <t>14,2%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-12,91; 99,02</t>
+          <t>-15,04; 99,01</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>19,48; 158,03</t>
+          <t>20,75; 159,12</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 114,36</t>
+          <t>0,13; 118,33</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-23,05; 65,67</t>
+          <t>-22,94; 57,6</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-23,35; 70,45</t>
+          <t>-21,72; 73,76</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-73,62; -3,34</t>
+          <t>-38,59; 24,34</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-10,97; 56,79</t>
+          <t>-9,71; 53,17</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>9,56; 87,17</t>
+          <t>8,81; 90,62</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-44,56; 23,24</t>
+          <t>-10,23; 48,15</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-0,88</t>
+          <t>1,02</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-0,23</t>
+          <t>-0,22</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-0,59</t>
+          <t>0,39</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 2,22</t>
+          <t>-2,83; 2,16</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 5,66</t>
+          <t>0,17; 5,62</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 2,08</t>
+          <t>-1,56; 3,46</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 1,97</t>
+          <t>-3,01; 1,82</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 5,6</t>
+          <t>-0,11; 5,27</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 2,07</t>
+          <t>-2,41; 2,04</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 1,32</t>
+          <t>-2,4; 1,27</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>0,66; 4,55</t>
+          <t>0,64; 4,53</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 1,19</t>
+          <t>-1,33; 2,14</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-13,24%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-3,55%</t>
+          <t>-3,27%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-8,97%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-35,47; 38,99</t>
+          <t>-36,07; 38,95</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 105,51</t>
+          <t>1,29; 103,21</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-67,11; 33,38</t>
+          <t>-19,05; 63,97</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-38,51; 40,77</t>
+          <t>-38,21; 35,57</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 107,57</t>
+          <t>-2,41; 97,61</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-32,4; 42,16</t>
+          <t>-29,64; 41,35</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-29,84; 24,74</t>
+          <t>-32,18; 21,22</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>8,41; 78,52</t>
+          <t>9,02; 78,04</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-47,44; 19,97</t>
+          <t>-17,68; 36,68</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3,03</t>
+          <t>3,65</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,43</t>
+          <t>1,04</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>1,7</t>
+          <t>2,31</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,49; 3,07</t>
+          <t>0,62; 3,06</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>1,97; 4,55</t>
+          <t>1,86; 4,31</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1,27; 4,45</t>
+          <t>2,41; 4,83</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,16</t>
+          <t>0,58; 3,12</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,89</t>
+          <t>0,29; 3,12</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 1,58</t>
+          <t>-0,05; 2,16</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>1,02; 2,79</t>
+          <t>0,95; 2,68</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>1,44; 3,23</t>
+          <t>1,44; 3,17</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,69</t>
+          <t>1,46; 3,07</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>64,47%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>37,13%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>8,88; 60,65</t>
+          <t>9,71; 58,84</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>30,48; 88,73</t>
+          <t>30,07; 84,61</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>20,49; 83,89</t>
+          <t>38,54; 92,21</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>8,86; 51,2</t>
+          <t>7,9; 50,77</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>3,73; 45,97</t>
+          <t>3,61; 50,65</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-17,19; 25,61</t>
+          <t>-0,5; 35,9</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>15,27; 47,76</t>
+          <t>14,23; 45,68</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>21,52; 55,8</t>
+          <t>21,24; 53,77</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>9,21; 46,0</t>
+          <t>22,0; 53,06</t>
         </is>
       </c>
     </row>
